--- a/lit_review_results/3-result_phase/review_results.xlsx
+++ b/lit_review_results/3-result_phase/review_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/3-result_phase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA16420-24B0-C84E-AC27-9FF8240961C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B250FAD8-3F52-F74D-A768-2BFA91E80FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7740" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="400">
   <si>
     <t>Database</t>
   </si>
@@ -705,15 +705,572 @@
   </si>
   <si>
     <t>https://www.sciencedirect.com/science/article/pii/S1389128615002728?pes=vor&amp;utm_source=scopus&amp;getft_integrator=scopus</t>
+  </si>
+  <si>
+    <t>Citation Search</t>
+  </si>
+  <si>
+    <t>https://jonathanmayer.org/publications/bau13.pdf</t>
+  </si>
+  <si>
+    <t>Bau, J., Mayer, J.R., Paskov, H.S., &amp; Mitchell, J.C.</t>
+  </si>
+  <si>
+    <t>W2SP</t>
+  </si>
+  <si>
+    <t>A Promising Direction for Web Tracking Countermeasures</t>
+  </si>
+  <si>
+    <t>Web tracking continues to pose a vexing policy problem. Surveys have repeatedly demonstrated substantial consumer demand for control mechanisms, and policymakers worldwide have pressed for a Do Not Track system that effectuates user preferences. At present, however, consumers are left in the lurch: existing control mechanisms and countermeasures have spotty effectiveness and are difficult to use. We argue in this position paper that machine learning could enable tracking countermeasures that are effective and easy to use. Moreover, by distancing human expert judgments, machine learning approaches are both easy to maintain and palatable to browser vendors. We briefly explore some of the promise and challenges of machine learning for tracking countermeasures, and we close with preliminary results from a prototype implementation.</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9484564</t>
+  </si>
+  <si>
+    <t>10.1109/INFOCOMWKSHPS51825.2021.9484564</t>
+  </si>
+  <si>
+    <t>Sun, Jingxue and Huang, Zhiqiu and Yang, Ting and Wang, Wengjie and Zhang, Yuqing</t>
+  </si>
+  <si>
+    <t>IEEE INFOCOM</t>
+  </si>
+  <si>
+    <t>A system for detecting third-party tracking through the combination of dynamic analysis and static analysis</t>
+  </si>
+  <si>
+    <t>With the continuous development of Internet technology, people pay more and more attention to private security. In particular, third-party tracking is a major factor affecting privacy security. So far, the most effective way to prevent third-party tracking is to create a blacklist. However, blacklist generation and maintenance need to be carried out manually which is inefficient and difficult to maintain. In order to generate blacklists more quickly and accurately in this era of big data, this paper proposes a machine learning system MFTrackerDetector against third-party tracking. The system is based on the theory of structural hole and only detects third-party trackers. The system consists of two subsystems, DMTrackerDetector and DFTrackerDetector. DMTrackerDetector is a JavaScript-based subsystem and DFTrackerDetector is a Flash-based subsystem. Because tracking code and non-tracking code often call different APIs, DMTrackerDetector builds a classifier using all the APIs in JavaScript as features and extracts the API features in JavaScript through dynamic analysis. Unlike static analysis method, the dynamic analysis method can effectively avoid code obfuscation. DMTrackerDetector eventually generates a JavaScript-based third-party tracker list named Jlist. DFTrackerDetector constructs a classifier using all the APIs in ActionScript as features and extracts the API features in the flash script through static analysis. DFTrackerDetector finally generates a Flash-based third-party tracker list named Flist. DFTrackerDetector achieved 92.98% accuracy in the Flash test set and DMTrackerDetector achieved 90.79% accuracy in the JavaScript test set. MFTrackerDetector eventually generates a list of third-party trackers, which is a combination of Jlist and Flist.</t>
+  </si>
+  <si>
+    <t>Web Security, Privacy, JavaScript, Flash, Third-Party Tracking, Machine Learning</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9984339</t>
+  </si>
+  <si>
+    <t>10.1109/ICCCNT54827.2022.9984339</t>
+  </si>
+  <si>
+    <t>M, Yadhu Krishna and S, Sanjana and G, Thushara M.</t>
+  </si>
+  <si>
+    <t>ICCCNT</t>
+  </si>
+  <si>
+    <t>Ad Service Detection - A Comparative Study Using Machine Learning Techniques</t>
+  </si>
+  <si>
+    <t>The use of web-based services has been soaring since the internet has come up. Hence, traditional forms of advertisements have moved on to the web, leading to a rising number of ad services and trackers affecting user privacy. Ad blockers were developed in order to prevent these. However, the currently available ad blockers are purely based on a predefined set of blacklist domains. This study proposes a machine learning-based approach to detect web-based ad services and trackers. In order to help us explore the area using machine learning techniques, a dataset was created. The developed dataset contained 74,000 entries comprising both domains that served advertisements and normal domains. In addition, we have also compared the scores that were obtained by various supervised machine learning models, and the best model was identified. The best model offered up to 88% accuracy in classifying ad services and normal websites. The model contributed by this paper could be further developed into a machine learning-based advertisement blocker system.</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/9152669</t>
+  </si>
+  <si>
+    <t>10.1109/SP40000.2020.00005</t>
+  </si>
+  <si>
+    <t>Iqbal, Umar and Snyder, Peter and Zhu, Shitong and Livshits, Benjamin and Qian, Zhiyun and Shafiq, Zubair</t>
+  </si>
+  <si>
+    <t>IEEE S&amp;P</t>
+  </si>
+  <si>
+    <t>AdGraph: A Graph-Based Approach to Ad and Tracker Blocking</t>
+  </si>
+  <si>
+    <t>User demand for blocking advertising and tracking online is large and growing. Existing tools, both deployed and described in research, have proven useful, but lack either the completeness or robustness needed for a general solution. Existing detection approaches generally focus on only one aspect of advertising or tracking (e.g. URL patterns, code structure), making existing approaches susceptible to evasion.In this work we present AdGraph, a novel graph-based machine learning approach for detecting advertising and tracking resources on the web. AdGraph differs from existing approaches by building a graph representation of the HTML structure, network requests, and JavaScript behavior of a webpage, and using this unique representation to train a classifier for identifying advertising and tracking resources. Because AdGraph considers many aspects of the context a network request takes place in, it is less susceptible to the single-factor evasion techniques that flummox existing approaches.We evaluate AdGraph on the Alexa top-10K websites, and find that it is highly accurate, able to replicate the labels of human-generated filter lists with 95.33% accuracy, and can even identify many mistakes in filter lists. We implement AdGraph as a modification to Chromium. AdGraph adds only minor overhead to page loading and execution, and is actually faster than stock Chromium on 42% of websites and AdBlock Plus on 78% of websites. Overall, we conclude that AdGraph is both accurate enough and performant enough for online use, breaking comparable or fewer websites than popular filter list based approaches.</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3694811.3697816</t>
+  </si>
+  <si>
+    <t>10.1145/3694811.3697816</t>
+  </si>
+  <si>
+    <t>Campeny-Roig, Eloi and Castell-Uroz, Ismael and Barlet-Ros, Pere</t>
+  </si>
+  <si>
+    <t>GNNET</t>
+  </si>
+  <si>
+    <t>AST-GNN: A Graph Neural Network for Web Tracking Detection</t>
+  </si>
+  <si>
+    <t>Web tracking technology is prevalent on the Internet today, with most websites employing user identification systems that can accurately identify users or devices behind browsers. While numerous works in literature attempt to create machine learning models for detecting these identification systems, many rely on features susceptible to obfuscation techniques and are only partially capable of identifying specific subsets of web tracking algorithms they were trained on. Additionally, classification is typically done over entire resources, making it difficult to distinguish between web tracking code and legitimate code within the same file. In this work, we propose AST-GNN, a graph neural network model applied to the abstract syntax tree structure of JavaScript files, which can predict portions of code used for tracking purposes. By focusing on the code structure, AST-GNN can detect various web tracking systems and it is robust against obfuscation techniques. Our results show that the system has an accuracy rate above 95% in identifying web tracking code snippets, with computation performance in the order of milliseconds, fast enough to be used in real-time.</t>
+  </si>
+  <si>
+    <t>Graph Neural Network, Web Tracking, Privacy</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/abs/10.1145/3658644.3670329</t>
+  </si>
+  <si>
+    <t>10.1145/3658644.3670329</t>
+  </si>
+  <si>
+    <t>Amjad, Abdul Haddi and Munir, Shaoor and Shafiq, Zubair and Gulzar, Muhammad Ali</t>
+  </si>
+  <si>
+    <t>CCS</t>
+  </si>
+  <si>
+    <t>Blocking Tracking JavaScript at the Function Granularity</t>
+  </si>
+  <si>
+    <t>Modern websites extensively rely on JavaScript to implement both functionality and tracking. Existing privacy-enhancing content-blocking tools struggle against mixed scripts, which simultaneously implement both functionality and tracking. Blocking such scripts would break functionality, and not blocking them would allow tracking. We propose Not.js, a fine-grained JavaScript blocking tool that operates at the function-level granularity. Not.js's strengths lie in analyzing the dynamic execution context, including the call stack and calling context of each JavaScript function, and then encoding this context to build a rich graph representation. Not.js trains a supervised machine learning classifier on a webpage's graph representation to first detect tracking at the function-level and then automatically generates surrogate scripts that preserve functionality while removing tracking. Our evaluation of Not.js on the top-10K websites demonstrates that it achieves high precision (94%) and recall (98%) in detecting tracking functions, outperforming the state-of-the-art while being robust against off-the-shelf JavaScript obfuscation. Fine-grained detection of tracking functions allows Not.js to automatically generate surrogate scripts, which our evaluation shows that successfully remove tracking functions without causing major breakage. Our deployment of Not.js shows that mixed scripts are present on 62.3% of the top-10K websites, with 70.6% of the mixed scripts being third-party that engage in tracking activities such as cookie ghostwriting.</t>
+  </si>
+  <si>
+    <t>privacy, web, software engineering, code refactoring</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3576915.3616586</t>
+  </si>
+  <si>
+    <t>10.1145/3576915.3616586</t>
+  </si>
+  <si>
+    <t>Shaoor Munir, Sandra Siby, Umar Iqbal, Steven Englehardt, Zubair Shafiq, Carmela Troncoso</t>
+  </si>
+  <si>
+    <t>COOKIEGRAPH: Measuring and Countering First-Party Tracking Cookies</t>
+  </si>
+  <si>
+    <t>As third-party cookie blocking is becoming the norm in mainstream web browsers, advertisers and trackers have started to use first-party cookies for tracking. To understand this phenomenon, we conduct a differential measurement study with versus without third-party cookies. We find that first-party cookies are used to store and exfiltrate identifiers to known trackers even when third-party cookies are blocked.
+As opposed to third-party cookie blocking, first-party cookie blocking is not practical because it would result in major breakage of website functionality. We propose CookieGraph, a machine learning-based approach that can accurately and robustly detect and block first-party tracking cookies. CookieGraph detects first-party tracking cookies with 90.18% accuracy, outperforming the state-of-the-art CookieBlock by 17.31%. We show that CookieGraph is robust against cookie name manipulation, while CookieBlock’s accuracy drops by 15.87%. While blocking all first-party cookies results in major breakage on 32% of the sites with SSO logins, and CookieBlock reduces it to 10%, we show that CookieGraph does not cause any major breakage on these sites.
+Our deployment of CookieGraph shows that first-party tracking cookies are used on 89.86% of the top-million websites. We find that 96.61% of these first-party tracking cookies are in fact ghostwritten by third-party scripts embedded in the first-party context. We also find evidence of first-party tracking cookies being set by fingerprinting scripts. The most prevalent first-party tracking cookies are set by major advertising entities such as Google, Facebook, and TikTok.</t>
+  </si>
+  <si>
+    <t>cookies, machine learning, privacy, tracking, web security</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9519497</t>
+  </si>
+  <si>
+    <t>10.1109/SP40001.2021.00007</t>
+  </si>
+  <si>
+    <t>Chen, Quan and Snyder, Peter and Livshits, Ben and Kapravelos, Alexandros</t>
+  </si>
+  <si>
+    <t>S&amp;P</t>
+  </si>
+  <si>
+    <t>Detecting Filter List Evasion with Event-Loop-Turn Granularity JavaScript Signatures</t>
+  </si>
+  <si>
+    <t>Content blocking is an important part of a per-formant, user-serving, privacy respecting web. Current content blockers work by building trust labels over URLs. While useful, this approach has many well understood shortcomings. Attackers may avoid detection by changing URLs or domains, bundling unwanted code with benign code, or inlining code in pages.The common flaw in existing approaches is that they evaluate code based on its delivery mechanism, not its behavior. In this work we address this problem by building a system for generating signatures of the privacy-and-security relevant behavior of executed JavaScript. Our system uses as the unit of analysis each script’s behavior during each turn on the JavaScript event loop. Focusing on event loop turns allows us to build highly identifying signatures for JavaScript code that are robust against code obfuscation, code bundling, URL modification, and other common evasions, as well as handle unique aspects of web applications.This work makes the following contributions to the problem of measuring and improving content blocking on the web: First, we design and implement a novel system to build per-event-loop-turn signatures of JavaScript behavior through deep instrumentation of the Blink and V8 runtimes. Second, we apply these signatures to measure how much privacy-and-security harming code is missed by current content blockers, by using EasyList and EasyPrivacy as ground truth and finding scripts that have the same privacy and security harming patterns. We build 1,995,444 signatures of privacy-and-security relevant behaviors from 11,212 unique scripts blocked by filter lists, and find 3,589 unique scripts hosting known harmful code, but missed by filter lists, affecting 12.48% of websites measured. Third, we provide a taxonomy of ways scripts avoid detection and quantify the occurrence of each. Finally, we present defenses against these evasions, in the form of filter list additions where possible, and through a proposed, signature based system in other cases.As part of this work, we share the implementation of our signature-generation system, the data gathered by applying that system to the Alexa 100K, and 586 AdBlock Plus compatible filter list rules to block instances of currently blocked code being moved to new URLs.</t>
+  </si>
+  <si>
+    <t>https://www.ndss-symposium.org/ndss-paper/fp-fed-privacy-preserving-federated-detection-of-browser-fingerprinting/</t>
+  </si>
+  <si>
+    <t>10.14722/ndss.2024.24360</t>
+  </si>
+  <si>
+    <t>Annamalai, Meenatchi and Bilogrevic, Igor and De Cristofaro, Emiliano</t>
+  </si>
+  <si>
+    <t>NDSS</t>
+  </si>
+  <si>
+    <t>Symposium</t>
+  </si>
+  <si>
+    <t>FP-Fed: Privacy-Preserving Federated Detection of Browser Fingerprinting</t>
+  </si>
+  <si>
+    <t>Browser fingerprinting often provides an attractive alternative to third-party cookies for tracking users across the web. In fact, the increasing restrictions on third-party cookies placed by common web browsers and recent regulations like the GDPR may accelerate the transition. To counter browser fingerprinting, previous work proposed a number of techniques to detect its prevalence and severity. However, most – if not all – of those techniques rely on 1) centralized web crawls and/or 2) computationally-intensive operations to extract and process signals (e.g., information-flow and static analysis).
+To address these limitations, we present FP-Fed, the first distributed system for browser fingerprinting detection. Using FP-Fed, users collaboratively train on-device models based on their real browsing patterns, without sharing their training data with a central entity, by relying on Differentially Private Federated Learning (DP-FL). To demonstrate its feasibility and effectiveness, we evaluate FP-Fed’s performance on a set of 20k popular websites with different privacy levels, numbers of participants, and features extracted from the scripts. Our experiments show that FP-Fed achieves reasonably high detection performance and can perform both training and inference efficiently, on-device, by only relying on runtime signals extracted from the execution trace, without requiring any resource-intensive operation.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.comnet.2019.106993</t>
+  </si>
+  <si>
+    <t>0.1016/j.comnet.2019.106993</t>
+  </si>
+  <si>
+    <t>Federico Cozza and Alfonso Guarino and Francesco Isernia and Delfina Malandrino and Antonio Rapuano and Raffaele Schiavone and Rocco Zaccagnino</t>
+  </si>
+  <si>
+    <t>Computer Networks</t>
+  </si>
+  <si>
+    <t>Hybrid and lightweight detection of third party tracking: Design, implementation, and evaluation</t>
+  </si>
+  <si>
+    <t>A common practice for websites is to rely on services provided by third party sites to track users and provide personalized experiences. Unfortunately, this practice has strong implications for both users and performance. From one hand, the privacy of individuals is at a risk given the use of valuable information used for the reconstruction of personal profiles. From the other hand, many existing countermeasures to protect privacy, having been implemented into Web browsers, exhibit performance issues, mainly due to the use of huge (and difficult to maintain up to date) lists of resources that have to be filtered out, given their privacy intrusiveness. To overcome these limitations, we propose the use of a hybrid mechanism exploiting blacklisting and machine learning for the automatic identification of privacy intrusive services requested while browsing Web pages. The idea is to use the blacklisting technique (widely used by the majority of privacy tools), in combination with a machine learning model which distinguishes between malicious and functional resources, and hence updates the blacklist, accordingly. We found out that machine learning models are able to classify JavaScript programs and HTTP requests with accuracy up to 91% and 97%, respectively. We provided a prototype implementation of this hybrid mechanism, named GuardOne, and we performed an exhaustive evaluation study to assess its effectiveness and performance. Results showed that GuardOne is able to filter out malicious resources from users’ requests without performance degradation when compared with traditional systems that leverage on the use of static lists for filtering. Moreover, results about effectiveness show that our mechanism, even with some small improvements, is able to efficiently filter out malicious requests and reduce in a substantial way personal information leakage.</t>
+  </si>
+  <si>
+    <t>https://www.usenix.org/conference/usenixsecurity22/presentation/iqbal</t>
+  </si>
+  <si>
+    <t>Umar Iqbal and Charlie Wolfe and Charles Nguyen and Steven Englehardt and Zubair Shafiq</t>
+  </si>
+  <si>
+    <t>USENIX</t>
+  </si>
+  <si>
+    <t>KHALEESI: Breaker of Advertising and Tracking Request Chains</t>
+  </si>
+  <si>
+    <t>Request chains are being used by advertisers and trackers for information sharing and circumventing recently introduced privacy protections in web browsers. There is little prior work on mitigating the increasing exploitation of request chains by advertisers and trackers. The state-of-the-art ad and tracker blocking approaches lack the necessary context to effectively detect advertising and tracking request chains. We propose Khaleesi, a machine learning approach that captures the essential sequential context needed to effectively detect advertising and tracking request chains. We show that Khaleesi achieves high accuracy, that holds well over time, is generally robust against evasion attempts, and outperforms existing approaches. We also show that Khaleesi is suitable for online deployment and it improves page load performance.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2478/popets-2021-0056</t>
+  </si>
+  <si>
+    <t>10.2478/popets-2021-0056</t>
+  </si>
+  <si>
+    <t>Nathan Reitinger, Michelle L. Mazurek</t>
+  </si>
+  <si>
+    <t>PoPETS</t>
+  </si>
+  <si>
+    <t>ML-CB: Machine Learning Canvas Block</t>
+  </si>
+  <si>
+    <t>With the aim of increasing online privacy,
+we present a novel, machine-learning based approach
+to blocking one of the three main ways website visitors are tracked online—canvas fingerprinting. Because
+the act of canvas fingerprinting uses, at its core, a
+JavaScript program, and because many of these programs are reused across the web, we are able to fit several machine learning models around a semantic representation of a potentially offending program, achieving
+accurate and robust classifiers. Our supervised learning approach is trained on a dataset we created by
+scraping roughly half a million websites using a custom Google Chrome extension storing information related to the canvas. Classification leverages our key insight that the images drawn by canvas fingerprinting
+programs have a facially distinct appearance, allowing
+us to manually classify files based on the images drawn;
+we take this approach one step further and train our
+classifiers not on the malleable images themselves, but
+on the more-difficult-to-change, underlying source code
+generating the images. As a result, ML-CB allows for
+more accurate tracker blocking.</t>
+  </si>
+  <si>
+    <t>Privacy, Device Fingerprinting, Web Measurement, Machine Learning</t>
+  </si>
+  <si>
+    <t>https://www.scitepress.org/Papers/2020/89720/</t>
+  </si>
+  <si>
+    <t>10.5220/0008972005320539</t>
+  </si>
+  <si>
+    <t>Alfonso Guarino and Delfina Malandrino and Rocco Zaccagnino and Federico Cozza and Antonio Rapuano</t>
+  </si>
+  <si>
+    <t>ICISSP</t>
+  </si>
+  <si>
+    <t>On Analyzing Third-party Tracking via Machine Learning</t>
+  </si>
+  <si>
+    <t>Nowadays, websites rely on services provided by third party sites to track users and offer personalized experiences. However, this practice threatens the privacy of individuals through the use of valuable information to create a digital personal profile. The existing client-side countermeasures to protect privacy, exhibit performance issues, mainly due to the use of blacklisting mechanisms (list of resources to be filtered out). In this paper, we study the use of machine learning methods to classify the thirdy-party privacy intrusive resources (trackers). To this end, we first downloaded (browsing Alexa’s Top 10 websites for each category like sports, shopping etc.) a dataset of 1000 web resources split into functional and tracking, and then we identified suitable metrics to distinguish between the two classes. In order to evaluate the effectiveness of the proposed metrics we have compared the performances of several machine learning models based on supervised learning among the most used in literature. As a result, we obtained that the Random Forest can classify functional and tracking resources with an accuracy of 91%.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3576915.3616637</t>
+  </si>
+  <si>
+    <t>10.1145/3576915.3616637</t>
+  </si>
+  <si>
+    <t>Ghasemisharif, Mohammad and Polakis, Jason</t>
+  </si>
+  <si>
+    <t>Read Between the Lines: Detecting Tracking JavaScript with Bytecode Classification</t>
+  </si>
+  <si>
+    <t>Browsers and extensions that aim to block online ads and tracking scripts predominantly rely on rules from filter lists for determining which resource requests must be blocked. These filter lists are often manually curated by a community of online users. However, due to the arms race between blockers and ad-supported websites, these rules must continuously get updated so as to adapt to novel bypassing techniques and modified requests, thus rendering the detection and rule-generation process cumbersome and reactive (which can result in major delays between propagation and detection). In this paper, we address the detection problem by proposing an automated pipeline that detects tracking and advertisement JavaScript resources with high accuracy, designed to incur minimal false positives and overhead. Our method models script detection as a text classification problem, where JavaScript resources are documents containing bytecode sequences. Since bytecode is directly obtained from the JavaScript interpreter, our technique is resilient against commonly used bypassing methods, such as URL randomization or code obfuscation. We experiment with both deep learning and traditional ML-based approaches for bytecode classification and show that our approach identifies ad/tracking scripts with 97.08% accuracy, significantly outperforming cutting-edge systems in terms of both precision and the level of required features. Our experimental analysis further highlights our system's capabilities, by demonstrating how it can augment filter lists by uncovering ad/tracking scripts that are currently unknown, as well as proactively detecting scripts that have been erroneously added by list curators.</t>
+  </si>
+  <si>
+    <t>Measurement; Web security; Privacy; Ad/tracking blocking</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/chapter/10.1007/978-981-96-0821-8_16</t>
+  </si>
+  <si>
+    <t>Wang, X., Liu, W., Zheng, C., Liu, X., Cao, Y., Liu, Q</t>
+  </si>
+  <si>
+    <t>ADMA</t>
+  </si>
+  <si>
+    <t>SDM-GAT: StylisticFP Detection Method Based on Graph Attention Network</t>
+  </si>
+  <si>
+    <t>Recent research has uncovered that CSS style sheets can be leveraged for user fingerprinting by probing various characteristics, thereby circumventing existing detection mechanisms and mitigation strategies-posing serious privacy concerns. In contrast to the extensively studied JavaScript-based fingerprinting, no dedicated detection techniques have been developed specifically for CSS-based tracking. Furthermore, the inherent nature of CSS code, which lacks data flow and control flow structures and execution capabilities, complicates the analysis. To bridge this gap, we propose SDM-GAT, a novel detection approach that employs a Graph Attention Network (GAT) with a multi-head attention mechanism to effectively analyze graphs derived from CSS style sheets. In light of the limitations of existing datasets, we built a comprehensive dataset by collecting CSS content from Alexa’s Top 10,000 websites and embedding StylisticFP tracking code into selected sites. Then, We converted CSS code into graph representations, pruned these graphs to reduce computational complexity, and applied GAT to classify and detect tracking CSS code with high accuracy. Experimental results indicate that SDM-GAT outperforms traditional detection methods, demonstrating superior recognition accuracy and generalization capacity. The model achieves an accuracy of 98.01% and an AUC of 0.98, making it the first effective detection technique targeting CSS-based tracking. This study provides valuable insights and opens new avenues for enhancing privacy protection in web environments.</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/2875475.2875479</t>
+  </si>
+  <si>
+    <t>10.1145/2875475.2875479</t>
+  </si>
+  <si>
+    <t>Kaizer, Andrew J. and Gupta, Minaxi</t>
+  </si>
+  <si>
+    <t>IWSPA'16</t>
+  </si>
+  <si>
+    <t>Towards Automatic Identification of JavaScript-oriented Machine-Based Tracking</t>
+  </si>
+  <si>
+    <t>Machine-based tracking is a type of behavior that extracts information on a user's machine, which can then be used for fingerprinting, tracking, or profiling purposes. In this paper, we focus on JavaScript-oriented machine-based tracking as JavaScript is widely accessible in all browsers. We find that coarse features related to JavaScript access, cookie access, and URL length subdomain information can perform well in creating a classifier that can identify these machine-based trackers with 97.7% accuracy. We then use the classifier on real-world datasets based on 30-minute website crawls of different types of websites -- including websites that target children and websites that target a popular audience -- and find 85%+ of all websites utilize machine-based tracking, even when they target a regulated group (children) as their primary audience.</t>
+  </si>
+  <si>
+    <t>https://petsymposium.org/popets/2017/popets-2017-0006.php</t>
+  </si>
+  <si>
+    <t>10.1515/popets-2017-0006</t>
+  </si>
+  <si>
+    <t>Ikram, M., Asghar, H.J., Kâafar, M.A., Mahanti, A., &amp; Krishnamurthy, B.</t>
+  </si>
+  <si>
+    <t>Towards Seamless Tracking-Free Web: Improved Detection of Trackers via One-class Learning</t>
+  </si>
+  <si>
+    <t>Numerous tools have been developed to aggressively block the execution of popular JavaScript programs in Web browsers. Such blocking also affects functionality of webpages and impairs user experience. As a consequence, many privacy preserving tools that have been developed to limit online tracking, often executed via JavaScript programs, may suffer from poor performance and limited uptake. A mechanism that can isolate JavaScript programs necessary for proper functioning of the website from tracking JavaScript programs would thus be useful. Through the use of a manually labelled dataset composed of 2,612 JavaScript programs, we show how current privacy preserving tools are ineffective in finding the right balance between blocking tracking JavaScript programs and allowing functional JavaScript code. To the best of our knowledge, this is the first study to assess the performance of current web privacy preserving tools in determining tracking vs. functional JavaScript programs. To improve this balance, we examine the two classes of JavaScript programs and hypothesize that tracking JavaScript programs share structural similarities that can be used to differentiate them from functional JavaScript programs. The rationale of our approach is that web developers often “borrow” and customize existing pieces of code in order to embed tracking (resp. functional) JavaScript programs into their webpages. We then propose one-class machine learning classifiers using syntactic and semantic features extracted from JavaScript programs. When trained only on samples of tracking JavaScript programs, our classifiers achieve accuracy of 99%, where the best of the privacy preserving tools achieve accuracy of 78%. The performance of our classifiers is comparable to that of traditional two-class SVM. One-class classification, where a training set of only tracking JavaScript programs is used for learning, has the advantage that it requires fewer labelled examples that can be obtained via manual inspection of public lists of well-known trackers. We further test our classifiers and several popular privacy preserving tools on a larger corpus of 4,084 web- sites with 135,656 JavaScript programs. The output of our best classifier on this data is between 20 to 64% different from the tools under study. We manually analyse a sample of the JavaScript programs for which our classifier is in disagreement with all other privacy preserving tools, and show that our approach is not only able to enhance user web experience by correctly classifying more functional JavaScript programs, but also discovers previously unknown tracking services.</t>
+  </si>
+  <si>
+    <t>Machine learning, one class SVM, pulearning, measurements, JavaScripts, tracking, privacy, usability, security</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/2872427.2883028</t>
+  </si>
+  <si>
+    <t>10.1145/2872427.2883028</t>
+  </si>
+  <si>
+    <t>Yu, Zhonghao and Macbeth, Sam and Modi, Konark and Pujol, Josep M.</t>
+  </si>
+  <si>
+    <t>WWW</t>
+  </si>
+  <si>
+    <t>Tracking the Trackers</t>
+  </si>
+  <si>
+    <t>Online tracking poses a serious privacy challenge that has drawn significant attention in both academia and industry. Existing approaches for preventing user tracking, based on curated blocklists, suffer from limited coverage and coarse-grained resolution for classification, rely on exceptions that impact sites' functionality and appearance, and require significant manual maintenance. In this paper we propose a novel approach, based on the concepts leveraged from $k$-Anonymity, in which users collectively identify unsafe data elements, which have the potential to identify uniquely an individual user, and remove them from requests.
+We deployed our system to 200,000 German users running the Cliqz Browser or the Cliqz Firefox extension to evaluate its efficiency and feasibility. Results indicate that our approach achieves better privacy protection than blocklists, as provided by Disconnect, while keeping the site breakage to a minimum, even lower than the community-optimized AdBlock Plus. We also provide evidence of the prevalence and reach of trackers to over 21 million pages of 350,000 unique sites, the largest scale empirical evaluation to date. 95% of the pages visited contain 3rd party requests to potential trackers and 78% attempt to transfer unsafe data. Tracker organizations are also ranked, showing that a single organization can reach up to 42% of all page visits in Germany.</t>
+  </si>
+  <si>
+    <t>Tracking, Data privacy, k-Anonymity, Privacy protection</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2478/popets-2021-0004</t>
+  </si>
+  <si>
+    <t>10.2478/popets-2021-0004</t>
+  </si>
+  <si>
+    <t>Valentino Rizzo, Stefano Traverso, Marco Mellia</t>
+  </si>
+  <si>
+    <t>Unveiling Web Fingerprinting in the Wild Via Code Mining and Machine Learning</t>
+  </si>
+  <si>
+    <t>Fueled by advertising companies’ need of accurately tracking users and their online habits, web fingerprinting practice has grown in recent years, with severe implications for users’ privacy. In this paper, we design, engineer and evaluate a methodology which combines the analysis of JavaScript code and machine learning for the automatic detection of web fingerprinters. We apply our methodology on a dataset of more than 400, 000 JavaScript files accessed by about 1, 000 volunteers during a one-month long experiment to observe adoption of fingerprinting in a real scenario. We compare approaches based on both static and dynamic code analysis to automatically detect fingerprinters and show they provide different angles complementing each other. This demonstrates that studies based on either static or dynamic code analysis provide partial view on actual fingerprinting usage in the web. To the best of our knowledge we are the first to perform this comparison with respect to fingerprinting. Our approach achieves 94% accuracy in small decision time. With this we spot more than 840 fingerprinting services, of which 695 are unknown to popular tracker blockers. These include new actual trackers as well as services which use fingerprinting for purposes other than tracking, such as anti-fraud and bot recognition.</t>
+  </si>
+  <si>
+    <t>Tracking, Fingerprinting, Machine Learning, Static Code Analysis, Dynamic Code Analysis</t>
+  </si>
+  <si>
+    <t>https://www.usenix.org/conference/usenixsecurity22/presentation/siby</t>
+  </si>
+  <si>
+    <t>Sandra Siby and Umar Iqbal and Steven Englehardt and Zubair Shafiq and Carmela Troncoso</t>
+  </si>
+  <si>
+    <t>WebGraph: Capturing Advertising and Tracking Information Flows for Robust Blocking</t>
+  </si>
+  <si>
+    <t>Users rely on ad and tracker blocking tools to protect their privacy. Unfortunately, existing ad and tracker blocking tools are susceptible to mutable advertising and tracking content. In this paper, we first demonstrate that a state-of-the-art ad and tracker blocker, AdGraph, is susceptible to such adversarial evasion techniques that are currently deployed on the web. Second, we introduce WebGraph, the first ML-based ad and tracker blocker that detects ads and trackers based on their action rather than their content. By featurizing the actions that are fundamental to advertising and tracking information flows – e.g., storing an identifier in the browser or sharing an identifier with another tracker – WebGraph performs nearly as well as prior approaches, but is significantly more robust to adversarial evasions. In particular, we show that WebGraph achieves comparable accuracy to AdGraph, while significantly decreasing the success rate of an adversary from near-perfect for AdGraph to around 8% for WebGraph. Finally, we show that WebGraph remains robust to sophisticated adversaries that use adversarial evasion techniques beyond those currently deployed on the web.</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3447535.3462549</t>
+  </si>
+  <si>
+    <t>10.1145/3447535.3462549</t>
+  </si>
+  <si>
+    <t>Kargaran, Amir Hossein and Akhondzadeh, Mohammad Sadegh and Heidarpour, Mohammad Reza and Manshaei, Mohammad Hossein and Salamatian, Kave and Nejad Sattary, Masoud</t>
+  </si>
+  <si>
+    <t>WebSci'21</t>
+  </si>
+  <si>
+    <t>Wide-AdGraph: Detecting Ad Trackers with a Wide Dependency Chain Graph</t>
+  </si>
+  <si>
+    <t>Websites use third-party ads and tracking services to deliver targeted ads and collect information about users that visit them. These services put users’ privacy at risk, and that is why users’ demand for blocking these services is growing. Most of the blocking solutions rely on crowd-sourced filter lists manually maintained by a large community of users. In this work, we seek to simplify the update of these filter lists by combining different websites through a large-scale graph connecting all resource requests made over a large set of sites. The features of this graph are extracted and used to train a machine learning algorithm with the aim of detecting ads and tracking resources. As our approach combines different information sources, it is more robust toward evasion techniques that use obfuscation or changing the usage patterns. We evaluate our work over the Alexa top-10K websites and find its accuracy to be 96.1% biased and 90.9% unbiased with high precision and recall. It can also block new ads and tracking services, which would necessitate being blocked by further crowd-sourced existing filter lists. Moreover, the approach followed in this paper sheds light on the ecosystem of third-party tracking and advertising.</t>
+  </si>
+  <si>
+    <t>Tracking, data privacy, ad blocking, filter lists, crowdsource</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/stamp/stamp.jsp?arnumber=8993052</t>
+  </si>
+  <si>
+    <t>10.1109/UEMCON47517.2019.8993052</t>
+  </si>
+  <si>
+    <t>T. Vo ─ C. Jaiswal</t>
+  </si>
+  <si>
+    <t>2019 IEEE 10th Annual Ubiquitous Computing, Electronics &amp; Mobile Communication Conference (UEMCON)</t>
+  </si>
+  <si>
+    <t>ADREMOVER: THE IMPROVED MACHINE LEARNING APPROACH FOR BLOCKING ADS</t>
+  </si>
+  <si>
+    <t>There is an explosion in the advertisements over web nowadays. Most of the websites we visit contain ads, even Facebook, Google and Twitter. Sometimes, it could also appear that someone is spying on us because there are incidents like ads that show up with the content exactly what you have been searching not long ago. Such events happen as a result of Web Tracking. Initially, ads were meant to support businesses and companies to market their products and persuade the users to purchase them. Web Tracker were meant to track the user interaction with the website so it can improve the user experience. However, some of these have allowed ads as malvertisements, which may take advantage of these functionalities to steal the users sensitive information. To counter this tsunami of ads (malware), several ad blockers were created and are freely available as a browser extension and serve the purpose of blocking ads and trackers and most of them use the hand-crafted filter lists, some of them apply the machine learning approach. However, because of outdated filter-list or white-list and also inability to identify brand new ad signatures, most of them do not provide the depth of functionality and intelligence required to block all the undesirable content. After applying several machine learning approaches and comparing them, we propose our tool, AdRemover, that is a novel approach using the list of URLs which contains Ad and Non-Ad as the dataset. The classification applying Random Forest exceeds 98% with the splitted 20% testing data and 80% training data from our dataset.</t>
+  </si>
+  <si>
+    <t>Security ─Machine Learning ─Adblock ─Malver-tisement ─Malware</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3623382</t>
+  </si>
+  <si>
+    <t>10.1145/3623382</t>
+  </si>
+  <si>
+    <t>Ahmad, Zubair ─ Casarin, Samuele ─ Calzavara, Stefano</t>
+  </si>
+  <si>
+    <t>ACM Trans. Web</t>
+  </si>
+  <si>
+    <t>An Empirical Analysis of Web Storage and Its Applications to Web Tracking</t>
+  </si>
+  <si>
+    <t>In this article, we present a large-scale empirical analysis of the use of web storage in the wild.By using dynamic taint tracking at the level of JavaScript and by performing an automated classification of the detected information flows, we shed light on the key characteristics of web storage uses in the Tranco Top 10k. Our analysis shows that web storage is routinely accessed by third parties, including known web trackers, who are particularly eager to have both read and write access to persistent web storage information. We then deep dive in web tracking as a prominent case study: our analysis shows that web storage is not yet as popular as cookies for tracking purposes ─ however, taint tracking is useful to detect potential new trackers not included in standard filter lists. Moreover, we observe that many websites do not comply with the General Data Protection Regulation directives when it comes to their use of web storage.</t>
+  </si>
+  <si>
+    <t>web tracking ─ JavaScript ─ taint analysis ─ web storage</t>
+  </si>
+  <si>
+    <t>http://link.springer.com/chapter/10.1007/978-3-319-20810-7_21</t>
+  </si>
+  <si>
+    <t>10.1007/978-3-319-20810-7_21</t>
+  </si>
+  <si>
+    <t>Amin FaizKhademiMohammad ZulkernineKomminist Weldemariam</t>
+  </si>
+  <si>
+    <t>DBSec 2015</t>
+  </si>
+  <si>
+    <t>FPGuard: Detection and Prevention of Browser Fingerprinting</t>
+  </si>
+  <si>
+    <t>Fingerprinting is an identification method used by enterprises to personalize services for their end-users and detect online fraud or by adversaries to launch targeted attacks. Various tools have been proposed to protect online users from undesired identification probes to enhance the privacy and security of the users. However, we have observed that new fingerprinting methods can easily evade the existing protection mechanisms. This paper presents a runtime fingerprinting detection and prevention approach, called FPGuard. FPGuard relies on the analysis of predefined metrics to identify fingerprinting attempts. While FPGuard’s detection capability is evaluated using the top 10,000 Alexa websites, its prevention mechanism is evaluated against four fingerprinting providers. Our evaluation results show that FPGuard can effectively recognize and mitigate fingerprinting-related activities and distinguish normal from abnormal webpages (or fingerprinters).</t>
+  </si>
+  <si>
+    <t>fingerprinting, user privacy, detection, prevention, FPGuard</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/stamp/stamp.jsp?arnumber=10230168</t>
+  </si>
+  <si>
+    <t>10.1109/ICCCN58024.2023.10230168</t>
+  </si>
+  <si>
+    <t>R. Zhao</t>
+  </si>
+  <si>
+    <t>2023 32nd International Conference on Computer Communications and Networks (ICCCN)</t>
+  </si>
+  <si>
+    <t>FProbe: The Flow-Centric Detection and a Large-Scale Measurement of Browser Fingerprinting</t>
+  </si>
+  <si>
+    <t>Browser fingerprinting has been used by websites for advertising and analytics. It uses JavaScript objects and APIs to collect browser attributes and generate unique identifiers for tracking online users. A few research works have been proposed to detect browser fingerprinting. They focused on the browser's built-in JavaScript objects and APIs that are invoked to retrieve browser attribute values but ignored the use of browser attributes in scripts. In this paper, we define the behavior of browser fingerprinting as aggregating different types of browser attributes, and reduce browser fingerprinting detection to a joint analysis of data flows of browser attribute values in JavaScript code. We propose a flow-centric browser fingerprinting detection framework, FProbe, which performs context-sensitive static data flow analysis of JavaScript code. We implemented FProbe in Java and evaluated it using 4,296 fingerprinting scripts from the recent work and 2,335,317 pieces of JavaScript code from 988,220 websites. FProbe achieved 97.81% and 96.31% F-measure on them, respectively. It identified browser fingerprinting behavior on 0.78% of the 988,220 websites. Only 72 fingerprinting scripts and 10 fingerprinting providers identified by FProbe were reported in previous work. The results show that FProbe is effective in detecting browser fingerprinting and complementary to existing detection tools.</t>
+  </si>
+  <si>
+    <t>security ─browser fingerprinting ─detection</t>
+  </si>
+  <si>
+    <t>https://www.scitepress.org/Link.aspx?doi=10.5220/0011965600003555</t>
+  </si>
+  <si>
+    <t>10.5220/0011965600003555</t>
+  </si>
+  <si>
+    <t>Polčák L. ─ Saloň M. ─ Maone G. ─ Hranický R. ─ McMahon M.</t>
+  </si>
+  <si>
+    <t>20th International Conference on Security and Cryptography, SECRYPT 2023</t>
+  </si>
+  <si>
+    <t>JShelter: Give Me My Browser Back</t>
+  </si>
+  <si>
+    <t>The web is used daily by billions. Even so, users are not protected from many threats by default. This paper builds on previous web privacy and security research and introduces JShelter, a webextension that fights to return the browser to users. Moreover, we introduce a library helping with common webextension development tasks and fixing loopholes. JShelter focuses on fingerprinting prevention, limitations of rich web APIs, prevention of attacks connected to timing, and learning information about the device, the browser, the user, and the surrounding physical environment and location. During the research of sensor APIs, we discovered a loophole in the sensor timestamps that lets any page observe the device boot time if sensor APIs are enabled in Chromium-based browsers. JShelter provides a fingerprinting report and other feedback that can be used by future web privacy research. Thousands of users around the world use the webextension every day. © 2023 by SCITEPRESS - Science and Technology Publications, Lda. Under CC license (CC BY-NC-ND 4.0).</t>
+  </si>
+  <si>
+    <t>Browser Fingerprinting ─ JavaScript ─ Web Privacy ─ Web Security ─ Webextension APIs</t>
+  </si>
+  <si>
+    <t>http://link.springer.com/chapter/10.1007/978-3-319-93411-2_13</t>
+  </si>
+  <si>
+    <t>10.1007/978-3-319-93411-2_13</t>
+  </si>
+  <si>
+    <t>Iskander Sanchez-RolaIgor Santos</t>
+  </si>
+  <si>
+    <t>DIMVA 2018</t>
+  </si>
+  <si>
+    <t>Knockin’ on Trackers’ Door: Large-Scale Automatic Analysis of Web Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this paper, we present the first generic large-scale analysis of different known and unknown web tracking scripts on the Internet to understand its current ecosystem and their behavior. To this end, we implemented TRACKINGINSPECTOR the first automatic method capable of detecting generically different types of web tracking scripts. This method automatically retrieves the existing scripts from a website and, through code similarity and machine learning, detects modifications of known tracking scripts and discovers unknown tracking script candidates.
+TRACKINGINSPECTOR analyzed the Alexa top 1M websites, computing the web tracking prevalence and its ecosystem, as well as the influence of hosting, website category, and website reputation. More than 90% websites performed some sort of tracking and more than 50% scripts were used for web tracking. Over 2,000,000 versions of known tracking scripts were found. We discovered several script renaming techniques used to avoid blacklists, performing a comprehensive analysis of them. 5,500,000 completely unknown likely tracking scripts were found, including more than 700 new different potential device fingerprinting unique scripts. Our system also automatically detected the fingerprinting behavior of a previously reported targeted fingerprinting-driven malware campaign in two different websites not previously documented.
+</t>
+  </si>
+  <si>
+    <t>device fingerprinting, privacy, web tracking</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.56553/popets-2024-0048</t>
+  </si>
+  <si>
+    <t>10.56553/popets-2024-0048</t>
+  </si>
+  <si>
+    <t>Sebastian Zimmeck, Daniel Goldelman, Owen Kaplan, Logan Brown, Justin Casler, Judeley Jean-Charles, Joe Champeau, Hamza Harkous </t>
+  </si>
+  <si>
+    <t>Website Data Transparency in the Browser</t>
+  </si>
+  <si>
+    <t>Data collection by websites and their integrated third parties is often not transparent. We design privacy interfaces for the browser to help people understand who is collecting which data from them. In a proof of concept browser extension, Privacy Pioneer, we implement a privacy popup, a privacy history interface, and a watchlist to notify people when their data is collected. For detecting location data collection, we develop a machine learning model based on TinyBERT, which reaches an average F1 score of 0.94. We supplement our model with deterministic methods to detect trackers, collection of personal data, and other monetization techniques. In a usability study with 100 participants 82% found Privacy Pioneer easy to understand and 90% found it useful indicating the value of privacy interfaces directly integrated in the browser.</t>
+  </si>
+  <si>
+    <t>Web Privacy, Data Transparency, Privacy Dashboards, Notice and Choice, Consent, Privacy Labels, Usability, Privacy Enhancing Technologies, Web Traffic Analysis, BERT, Machine Learning</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -751,6 +1308,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -784,7 +1347,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -905,73 +1468,107 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1286,7 +1883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -1334,7 +1931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1524,7 +2121,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1620,7 +2217,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -2278,9 +2875,1235 @@
         <v>207</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2013</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="173" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E35" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E40" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" s="21"/>
+      <c r="D46" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2025</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2016</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2017</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2016</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="C51" s="21"/>
+      <c r="D51" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H51" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2019</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2015</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2018</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="13"/>
+    </row>
+    <row r="63" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="13"/>
+    </row>
+    <row r="64" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="13"/>
+    </row>
+    <row r="72" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="13"/>
+    </row>
+    <row r="73" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="13"/>
+    </row>
+    <row r="79" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="13"/>
+    </row>
+    <row r="81" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="13"/>
+    </row>
+    <row r="82" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="13"/>
+    </row>
+    <row r="83" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="13"/>
+    </row>
+    <row r="84" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="13"/>
+    </row>
+    <row r="85" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="13"/>
+    </row>
+    <row r="86" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{FBEE8BCA-AECD-7640-A41B-621FBF8A8D39}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{5963C436-C4F5-844F-A96E-490C7B820BD2}"/>
@@ -2314,6 +4137,32 @@
     <hyperlink ref="B29" r:id="rId30" xr:uid="{1E46268F-3CD1-6F43-8D40-D64B2D9B574A}"/>
     <hyperlink ref="B30" r:id="rId31" xr:uid="{F83F8EF1-4A69-D04E-8AB4-AFCA4754E92F}"/>
     <hyperlink ref="B31" r:id="rId32" xr:uid="{B1D83E8A-D1B8-F849-9BB2-7C7BD4AFCF4C}"/>
+    <hyperlink ref="B33" r:id="rId33" xr:uid="{B56546E9-6AB3-C441-B5A5-620915CF16F3}"/>
+    <hyperlink ref="B32" r:id="rId34" xr:uid="{33C44AAB-54F3-064C-B57E-0911876AFF16}"/>
+    <hyperlink ref="B34" r:id="rId35" xr:uid="{7C61480F-E987-614C-A1C3-F9573A4E9ED9}"/>
+    <hyperlink ref="B35" r:id="rId36" xr:uid="{E201EB95-B887-1542-BE7D-1DF51E322B9D}"/>
+    <hyperlink ref="B36" r:id="rId37" xr:uid="{1D9962F5-6F90-EC48-BA21-A1AD459C9C88}"/>
+    <hyperlink ref="B37" r:id="rId38" xr:uid="{A932D233-B393-474A-8A3A-188BAEC14B17}"/>
+    <hyperlink ref="B38" r:id="rId39" xr:uid="{A1FA089F-0F58-C74C-96E7-1B159C8666EF}"/>
+    <hyperlink ref="B39" r:id="rId40" xr:uid="{0172150D-FDC5-6044-82A1-F103134C7409}"/>
+    <hyperlink ref="B40" r:id="rId41" xr:uid="{E6E24CEC-E1C4-DA46-AD1C-E6F6DD0F7489}"/>
+    <hyperlink ref="B41" r:id="rId42" xr:uid="{B6519244-149C-B24B-81B0-3A9CE41B81BF}"/>
+    <hyperlink ref="B42" r:id="rId43" xr:uid="{C951127D-AFCB-4F48-9032-0A52456D0638}"/>
+    <hyperlink ref="B43" r:id="rId44" xr:uid="{8488A576-4D70-5946-91AE-4E9538AD860D}"/>
+    <hyperlink ref="B47" r:id="rId45" xr:uid="{8198207C-D981-494D-A15E-5F27266FBA94}"/>
+    <hyperlink ref="B44" r:id="rId46" xr:uid="{53DBB112-FA8C-984E-81CB-AE0AD56E3C03}"/>
+    <hyperlink ref="B45" r:id="rId47" xr:uid="{BCDE4810-5275-E444-A25B-6C525D4CBCD4}"/>
+    <hyperlink ref="B46" r:id="rId48" xr:uid="{1BE49F85-FBDE-E84C-8D43-4D5887826407}"/>
+    <hyperlink ref="B50" r:id="rId49" xr:uid="{7F6379F0-AAA6-274B-B1D4-11232332C73A}"/>
+    <hyperlink ref="B49" r:id="rId50" xr:uid="{89199ED0-08B0-614F-92A5-5A041CC1A6D7}"/>
+    <hyperlink ref="B52" r:id="rId51" xr:uid="{B1B04A3B-BF2E-FB4F-92FC-CE85A3EDF6E7}"/>
+    <hyperlink ref="B53" r:id="rId52" xr:uid="{55E57EE3-8F32-2D4B-BD9C-0F1971227CB6}"/>
+    <hyperlink ref="B54" r:id="rId53" xr:uid="{9126161A-8134-8241-9177-DDC3EC71D511}"/>
+    <hyperlink ref="B55" r:id="rId54" xr:uid="{F7A8B56C-ADD9-984A-AC4B-6DA7DC6A4389}"/>
+    <hyperlink ref="B56" r:id="rId55" xr:uid="{E0A8F2A0-C9A8-5249-8CD1-E30BBEEB0A51}"/>
+    <hyperlink ref="B58" r:id="rId56" xr:uid="{50EDE256-2CB6-9A4E-B8A7-B0BBE5499DB8}"/>
+    <hyperlink ref="B57" r:id="rId57" xr:uid="{CE7020DD-E644-D940-A60D-43710686C621}"/>
+    <hyperlink ref="B59" r:id="rId58" xr:uid="{F9F21664-7DC3-8740-9C05-A52C5B200CE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/lit_review_results/3-result_phase/review_results.xlsx
+++ b/lit_review_results/3-result_phase/review_results.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/3-result_phase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B250FAD8-3F52-F74D-A768-2BFA91E80FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249B47F0-C400-7842-9B21-00D0211C816E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7740" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17360" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$90</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="407">
   <si>
     <t>Database</t>
   </si>
@@ -1255,6 +1255,27 @@
   </si>
   <si>
     <t>Web Privacy, Data Transparency, Privacy Dashboards, Notice and Choice, Consent, Privacy Labels, Usability, Privacy Enhancing Technologies, Web Traffic Analysis, BERT, Machine Learning</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10850137</t>
+  </si>
+  <si>
+    <t>10.1109/IPCCC59868.2024.10850137</t>
+  </si>
+  <si>
+    <t>Yuan, Yong and Wei, Ziling and Liu, Lin and Chen, Shuhui and Su, Jinshu</t>
+  </si>
+  <si>
+    <t>IPCCC</t>
+  </si>
+  <si>
+    <t>AST-Trans: Detecting Web Tracking using Transformer-based Deep Learning with Abstract Syntax Tree</t>
+  </si>
+  <si>
+    <t>Web tracking has become a key tool for service providers to collect online data and analyze user behaviors, raising concerns about the privacy of Internet users. In this paper, we propose a new web tracking detection method, namely AST-Trans, which detects and removes web tracking behavior using Transformer-based deep learning with abstract syntax trees. In the method, the abstract syntax tree is built for the detected website codes. Then, a sequence generation algorithm is proposed to convert tree-like code structures into one-dimensional sequences for deep models. To enhance training efficiency, we devise a reduction strategy to simplify the code tree structure by introducing equivalent nodes. After that, a Transformer-based deep learning algorithm is introduced to realize web tracking detection. By the proposed method, the exact tracking code blocks can be identified, and thus, we can implement the tracking code removal with minimum website breakage. To verify the effectiveness of the proposed method, an HTTPS proxy with AST-Trans on it is implemented to detect and remove tracking codes. We evaluate AST-Trans with the TrackSign-labeled dataset. The results show that the proposed method can detect the tracking behavior with high precision. In addition, we validate the feasibility of the method by measuring the website page breakage.</t>
+  </si>
+  <si>
+    <t>Web Tracking, Abstract Syntax Tree, Deep learning, Transformer</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1521,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1569,6 +1590,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1993,1404 +2021,1406 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>47</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="21"/>
       <c r="D4" s="3" t="s">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>138</v>
+        <v>227</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="J4" s="13"/>
+    </row>
+    <row r="5" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>19</v>
+        <v>223</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>229</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>106</v>
+        <v>2021</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>167</v>
+        <v>233</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>234</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="173" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>40</v>
+        <v>223</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>236</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>70</v>
+        <v>237</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>127</v>
+        <v>239</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2">
         <v>2023</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2019</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="B11" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2015</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="H11" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="B12" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="H13" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2016</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>25</v>
+      <c r="B14" s="19" t="s">
+        <v>400</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>52</v>
+        <v>401</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="E14" s="2">
         <v>2024</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>403</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>143</v>
+        <v>404</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>173</v>
+        <v>405</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>71</v>
+        <v>28</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="2"/>
+        <v>2023</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="H15" s="11" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>220</v>
+        <v>10</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2">
         <v>2023</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>36</v>
+        <v>14</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E17" s="2">
+        <v>2025</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2">
         <v>2021</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2016</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E20" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="2">
         <v>2023</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="F21" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="H21" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="2">
         <v>2024</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="J21" s="13"/>
-    </row>
-    <row r="22" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="2">
-        <v>2023</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>50</v>
+        <v>223</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>269</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="E23" s="2">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>141</v>
+        <v>272</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>222</v>
+        <v>12</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>71</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E26" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="2"/>
       <c r="H26" s="11" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>199</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>220</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E27" s="2">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="J27" s="13"/>
+        <v>186</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E28" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2024</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2015</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="B32" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2023</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2010</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E32" s="2">
-        <v>2013</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="H32" s="11" t="s">
-        <v>227</v>
+        <v>377</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J32" s="13"/>
-    </row>
-    <row r="33" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>232</v>
+        <v>2020</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>284</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="173" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J33" s="13"/>
+    </row>
+    <row r="34" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>236</v>
+        <v>380</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>237</v>
+        <v>381</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>238</v>
+        <v>382</v>
       </c>
       <c r="E34" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>239</v>
+        <v>383</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="J34" s="23"/>
-    </row>
-    <row r="35" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>243</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C35" s="21"/>
       <c r="D35" s="3" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="E35" s="2">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="J35" s="13"/>
     </row>
-    <row r="36" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>248</v>
+        <v>11</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>387</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>249</v>
+        <v>388</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>250</v>
+        <v>389</v>
       </c>
       <c r="E36" s="2">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>251</v>
+        <v>390</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>252</v>
+        <v>391</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>253</v>
+        <v>392</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>255</v>
+        <v>11</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>256</v>
+        <v>51</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>258</v>
+        <v>110</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>259</v>
+        <v>142</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="E38" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="2">
         <v>2023</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E39" s="2">
-        <v>2021</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>271</v>
+        <v>103</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="J39" s="13"/>
-    </row>
-    <row r="40" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="E40" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="2">
         <v>2024</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="I40" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" spans="1:10" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E41" s="2">
-        <v>2020</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="2"/>
       <c r="H41" s="11" t="s">
-        <v>285</v>
+        <v>163</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>286</v>
+        <v>193</v>
       </c>
       <c r="J41" s="13"/>
     </row>
-    <row r="42" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C42" s="21"/>
+        <v>305</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>306</v>
+      </c>
       <c r="D42" s="3" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="E42" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J42" s="13"/>
-    </row>
-    <row r="43" spans="1:10" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>293</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C43" s="21"/>
       <c r="D43" s="3" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="E43" s="2">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>300</v>
+        <v>66</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E44" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>128</v>
+        <v>96</v>
+      </c>
+      <c r="E44" s="26">
+        <v>2023</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>133</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>303</v>
+        <v>157</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="J44" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="E45" s="2">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B46" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="C46" s="21"/>
+      <c r="B46" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>323</v>
+      </c>
       <c r="D46" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E46" s="2">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="J46" s="13"/>
-    </row>
-    <row r="47" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>316</v>
+        <v>11</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>23</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>317</v>
+        <v>50</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>319</v>
+        <v>109</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>320</v>
+        <v>141</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="J47" s="13"/>
-    </row>
-    <row r="48" spans="1:10" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>322</v>
+        <v>13</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>222</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>323</v>
+        <v>67</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>324</v>
+        <v>97</v>
       </c>
       <c r="E48" s="2">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>325</v>
+        <v>158</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>326</v>
+        <v>188</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>327</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3425,333 +3455,351 @@
         <v>334</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>335</v>
+        <v>12</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>27</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>336</v>
+        <v>54</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2">
         <v>2021</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>129</v>
+        <v>113</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>338</v>
+        <v>145</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>339</v>
+        <v>175</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="C51" s="21"/>
+        <v>21</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="D51" s="3" t="s">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="E51" s="2">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>128</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>343</v>
+        <v>139</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2015</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H52" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B52" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E52" s="2">
+      <c r="B53" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E53" s="2">
         <v>2021</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H52" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="F53" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E53" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="B54" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2020</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="E54" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="H54" s="11" t="s">
-        <v>363</v>
+        <v>144</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>364</v>
+        <v>174</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>366</v>
+        <v>35</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>367</v>
+        <v>62</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>368</v>
+        <v>92</v>
       </c>
       <c r="E55" s="2">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>369</v>
+        <v>121</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>370</v>
+        <v>153</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>371</v>
+        <v>183</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>373</v>
+        <v>30</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>374</v>
+        <v>57</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>375</v>
+        <v>87</v>
       </c>
       <c r="E56" s="2">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>376</v>
+        <v>116</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>377</v>
+        <v>148</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>378</v>
+        <v>178</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>381</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="C57" s="21"/>
       <c r="D57" s="3" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="E57" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>383</v>
+        <v>289</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>387</v>
+        <v>14</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>394</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="E58" s="2">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>390</v>
+        <v>127</v>
       </c>
       <c r="G58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2021</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H58" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>394</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E59" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="H59" s="11" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="13"/>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H60" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="61" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
@@ -4103,66 +4151,71 @@
     </row>
     <row r="90" spans="1:10" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <autoFilter ref="A1:J90" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J90">
+      <sortCondition ref="H1:H90"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{FBEE8BCA-AECD-7640-A41B-621FBF8A8D39}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{5963C436-C4F5-844F-A96E-490C7B820BD2}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{9A0CE8E7-0B2D-8B47-84B0-E05C13DD27D5}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{2DFDB1D0-5722-AF42-91AB-B6E5B894FDE5}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{B4DCEB83-F5F0-A444-A7F2-236C71500780}"/>
-    <hyperlink ref="B8" r:id="rId6" xr:uid="{C44B9201-22DF-6747-8B76-91E70962F71E}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{BC7EDBEE-E6AA-6149-ABE0-854B7A10E657}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{D2B1D08E-FAC8-1342-87D4-504E4655AD3F}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{6E9352F0-ABD8-BA4E-9548-E2C1DD9DE809}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{476957A0-1070-B149-8053-A4817D7BEF4F}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{D0E10732-AE56-8841-B6DB-59813AB63364}"/>
-    <hyperlink ref="B14" r:id="rId12" xr:uid="{73558581-11B6-EE4C-88D6-FF9F538C9B05}"/>
-    <hyperlink ref="B13" r:id="rId13" xr:uid="{E067F151-CE8B-7A4B-91AE-71B6A800170E}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{2AE94C7D-C8FB-B64F-A79F-B60E2E2B3C2E}"/>
-    <hyperlink ref="C15" r:id="rId15" xr:uid="{46037573-973B-D841-941A-007153D72C53}"/>
-    <hyperlink ref="B16" r:id="rId16" xr:uid="{C7D50EF9-0AC7-454C-81EF-56029A1C461C}"/>
-    <hyperlink ref="B17" r:id="rId17" xr:uid="{78734F4D-7CD0-D24A-8726-4D952BD2FF45}"/>
-    <hyperlink ref="B18" r:id="rId18" xr:uid="{F44C2BC9-26F2-0C45-A1E1-98FCA441CD7C}"/>
-    <hyperlink ref="B19" r:id="rId19" xr:uid="{B206B80B-36AD-B748-8160-23061BAFB0D9}"/>
-    <hyperlink ref="B20" r:id="rId20" xr:uid="{B9E38A9E-5D79-214C-82FC-1F6DC1F50DBD}"/>
-    <hyperlink ref="B21" r:id="rId21" xr:uid="{3285D1FD-B415-B44E-9580-0FB5025A3E28}"/>
-    <hyperlink ref="C21" r:id="rId22" xr:uid="{CA412EC4-B94A-E94C-BFF7-99779B2805C4}"/>
-    <hyperlink ref="B22" r:id="rId23" xr:uid="{17AC8905-E862-4549-9CD1-6F60E5AFFEE1}"/>
-    <hyperlink ref="B23" r:id="rId24" xr:uid="{54D73695-69DB-114C-94AB-73CCB0EF94B2}"/>
-    <hyperlink ref="B24" r:id="rId25" xr:uid="{B20962CF-2622-2342-B9C5-A9FD7CC2E9BD}"/>
-    <hyperlink ref="B26" r:id="rId26" xr:uid="{78CC0CDC-1E3D-DD4D-9D8E-B6794E510778}"/>
-    <hyperlink ref="B25" r:id="rId27" xr:uid="{3B96D692-52CA-5249-976C-A1FD66867EA9}"/>
-    <hyperlink ref="B27" r:id="rId28" xr:uid="{6BC62555-5F9B-A247-A346-AA0D3872A748}"/>
-    <hyperlink ref="B28" r:id="rId29" xr:uid="{535A3AB4-F878-E345-9B1D-8E2F7C4A31C8}"/>
-    <hyperlink ref="B29" r:id="rId30" xr:uid="{1E46268F-3CD1-6F43-8D40-D64B2D9B574A}"/>
-    <hyperlink ref="B30" r:id="rId31" xr:uid="{F83F8EF1-4A69-D04E-8AB4-AFCA4754E92F}"/>
-    <hyperlink ref="B31" r:id="rId32" xr:uid="{B1D83E8A-D1B8-F849-9BB2-7C7BD4AFCF4C}"/>
-    <hyperlink ref="B33" r:id="rId33" xr:uid="{B56546E9-6AB3-C441-B5A5-620915CF16F3}"/>
-    <hyperlink ref="B32" r:id="rId34" xr:uid="{33C44AAB-54F3-064C-B57E-0911876AFF16}"/>
-    <hyperlink ref="B34" r:id="rId35" xr:uid="{7C61480F-E987-614C-A1C3-F9573A4E9ED9}"/>
-    <hyperlink ref="B35" r:id="rId36" xr:uid="{E201EB95-B887-1542-BE7D-1DF51E322B9D}"/>
-    <hyperlink ref="B36" r:id="rId37" xr:uid="{1D9962F5-6F90-EC48-BA21-A1AD459C9C88}"/>
-    <hyperlink ref="B37" r:id="rId38" xr:uid="{A932D233-B393-474A-8A3A-188BAEC14B17}"/>
-    <hyperlink ref="B38" r:id="rId39" xr:uid="{A1FA089F-0F58-C74C-96E7-1B159C8666EF}"/>
-    <hyperlink ref="B39" r:id="rId40" xr:uid="{0172150D-FDC5-6044-82A1-F103134C7409}"/>
-    <hyperlink ref="B40" r:id="rId41" xr:uid="{E6E24CEC-E1C4-DA46-AD1C-E6F6DD0F7489}"/>
-    <hyperlink ref="B41" r:id="rId42" xr:uid="{B6519244-149C-B24B-81B0-3A9CE41B81BF}"/>
-    <hyperlink ref="B42" r:id="rId43" xr:uid="{C951127D-AFCB-4F48-9032-0A52456D0638}"/>
-    <hyperlink ref="B43" r:id="rId44" xr:uid="{8488A576-4D70-5946-91AE-4E9538AD860D}"/>
-    <hyperlink ref="B47" r:id="rId45" xr:uid="{8198207C-D981-494D-A15E-5F27266FBA94}"/>
-    <hyperlink ref="B44" r:id="rId46" xr:uid="{53DBB112-FA8C-984E-81CB-AE0AD56E3C03}"/>
-    <hyperlink ref="B45" r:id="rId47" xr:uid="{BCDE4810-5275-E444-A25B-6C525D4CBCD4}"/>
-    <hyperlink ref="B46" r:id="rId48" xr:uid="{1BE49F85-FBDE-E84C-8D43-4D5887826407}"/>
-    <hyperlink ref="B50" r:id="rId49" xr:uid="{7F6379F0-AAA6-274B-B1D4-11232332C73A}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{9A0CE8E7-0B2D-8B47-84B0-E05C13DD27D5}"/>
+    <hyperlink ref="B7" r:id="rId4" xr:uid="{2DFDB1D0-5722-AF42-91AB-B6E5B894FDE5}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{B4DCEB83-F5F0-A444-A7F2-236C71500780}"/>
+    <hyperlink ref="B16" r:id="rId6" xr:uid="{C44B9201-22DF-6747-8B76-91E70962F71E}"/>
+    <hyperlink ref="B15" r:id="rId7" xr:uid="{BC7EDBEE-E6AA-6149-ABE0-854B7A10E657}"/>
+    <hyperlink ref="B17" r:id="rId8" xr:uid="{D2B1D08E-FAC8-1342-87D4-504E4655AD3F}"/>
+    <hyperlink ref="B19" r:id="rId9" xr:uid="{6E9352F0-ABD8-BA4E-9548-E2C1DD9DE809}"/>
+    <hyperlink ref="B20" r:id="rId10" xr:uid="{476957A0-1070-B149-8053-A4817D7BEF4F}"/>
+    <hyperlink ref="B22" r:id="rId11" xr:uid="{D0E10732-AE56-8841-B6DB-59813AB63364}"/>
+    <hyperlink ref="B25" r:id="rId12" xr:uid="{73558581-11B6-EE4C-88D6-FF9F538C9B05}"/>
+    <hyperlink ref="B24" r:id="rId13" xr:uid="{E067F151-CE8B-7A4B-91AE-71B6A800170E}"/>
+    <hyperlink ref="B26" r:id="rId14" xr:uid="{2AE94C7D-C8FB-B64F-A79F-B60E2E2B3C2E}"/>
+    <hyperlink ref="C26" r:id="rId15" xr:uid="{46037573-973B-D841-941A-007153D72C53}"/>
+    <hyperlink ref="B27" r:id="rId16" xr:uid="{C7D50EF9-0AC7-454C-81EF-56029A1C461C}"/>
+    <hyperlink ref="B28" r:id="rId17" xr:uid="{78734F4D-7CD0-D24A-8726-4D952BD2FF45}"/>
+    <hyperlink ref="B30" r:id="rId18" xr:uid="{F44C2BC9-26F2-0C45-A1E1-98FCA441CD7C}"/>
+    <hyperlink ref="B37" r:id="rId19" xr:uid="{B206B80B-36AD-B748-8160-23061BAFB0D9}"/>
+    <hyperlink ref="B39" r:id="rId20" xr:uid="{B9E38A9E-5D79-214C-82FC-1F6DC1F50DBD}"/>
+    <hyperlink ref="B41" r:id="rId21" xr:uid="{3285D1FD-B415-B44E-9580-0FB5025A3E28}"/>
+    <hyperlink ref="C41" r:id="rId22" xr:uid="{CA412EC4-B94A-E94C-BFF7-99779B2805C4}"/>
+    <hyperlink ref="B44" r:id="rId23" xr:uid="{17AC8905-E862-4549-9CD1-6F60E5AFFEE1}"/>
+    <hyperlink ref="B47" r:id="rId24" xr:uid="{54D73695-69DB-114C-94AB-73CCB0EF94B2}"/>
+    <hyperlink ref="B48" r:id="rId25" xr:uid="{B20962CF-2622-2342-B9C5-A9FD7CC2E9BD}"/>
+    <hyperlink ref="B51" r:id="rId26" xr:uid="{78CC0CDC-1E3D-DD4D-9D8E-B6794E510778}"/>
+    <hyperlink ref="B50" r:id="rId27" xr:uid="{3B96D692-52CA-5249-976C-A1FD66867EA9}"/>
+    <hyperlink ref="B52" r:id="rId28" xr:uid="{6BC62555-5F9B-A247-A346-AA0D3872A748}"/>
+    <hyperlink ref="B54" r:id="rId29" xr:uid="{535A3AB4-F878-E345-9B1D-8E2F7C4A31C8}"/>
+    <hyperlink ref="B55" r:id="rId30" xr:uid="{1E46268F-3CD1-6F43-8D40-D64B2D9B574A}"/>
+    <hyperlink ref="B56" r:id="rId31" xr:uid="{F83F8EF1-4A69-D04E-8AB4-AFCA4754E92F}"/>
+    <hyperlink ref="B60" r:id="rId32" xr:uid="{B1D83E8A-D1B8-F849-9BB2-7C7BD4AFCF4C}"/>
+    <hyperlink ref="B5" r:id="rId33" xr:uid="{B56546E9-6AB3-C441-B5A5-620915CF16F3}"/>
+    <hyperlink ref="B4" r:id="rId34" xr:uid="{33C44AAB-54F3-064C-B57E-0911876AFF16}"/>
+    <hyperlink ref="B6" r:id="rId35" xr:uid="{7C61480F-E987-614C-A1C3-F9573A4E9ED9}"/>
+    <hyperlink ref="B9" r:id="rId36" xr:uid="{E201EB95-B887-1542-BE7D-1DF51E322B9D}"/>
+    <hyperlink ref="B13" r:id="rId37" xr:uid="{1D9962F5-6F90-EC48-BA21-A1AD459C9C88}"/>
+    <hyperlink ref="B18" r:id="rId38" xr:uid="{A932D233-B393-474A-8A3A-188BAEC14B17}"/>
+    <hyperlink ref="B21" r:id="rId39" xr:uid="{A1FA089F-0F58-C74C-96E7-1B159C8666EF}"/>
+    <hyperlink ref="B23" r:id="rId40" xr:uid="{0172150D-FDC5-6044-82A1-F103134C7409}"/>
+    <hyperlink ref="B29" r:id="rId41" xr:uid="{E6E24CEC-E1C4-DA46-AD1C-E6F6DD0F7489}"/>
+    <hyperlink ref="B33" r:id="rId42" xr:uid="{B6519244-149C-B24B-81B0-3A9CE41B81BF}"/>
+    <hyperlink ref="B35" r:id="rId43" xr:uid="{C951127D-AFCB-4F48-9032-0A52456D0638}"/>
+    <hyperlink ref="B38" r:id="rId44" xr:uid="{8488A576-4D70-5946-91AE-4E9538AD860D}"/>
+    <hyperlink ref="B45" r:id="rId45" xr:uid="{8198207C-D981-494D-A15E-5F27266FBA94}"/>
+    <hyperlink ref="B40" r:id="rId46" xr:uid="{53DBB112-FA8C-984E-81CB-AE0AD56E3C03}"/>
+    <hyperlink ref="B42" r:id="rId47" xr:uid="{BCDE4810-5275-E444-A25B-6C525D4CBCD4}"/>
+    <hyperlink ref="B43" r:id="rId48" xr:uid="{1BE49F85-FBDE-E84C-8D43-4D5887826407}"/>
+    <hyperlink ref="B53" r:id="rId49" xr:uid="{7F6379F0-AAA6-274B-B1D4-11232332C73A}"/>
     <hyperlink ref="B49" r:id="rId50" xr:uid="{89199ED0-08B0-614F-92A5-5A041CC1A6D7}"/>
-    <hyperlink ref="B52" r:id="rId51" xr:uid="{B1B04A3B-BF2E-FB4F-92FC-CE85A3EDF6E7}"/>
-    <hyperlink ref="B53" r:id="rId52" xr:uid="{55E57EE3-8F32-2D4B-BD9C-0F1971227CB6}"/>
-    <hyperlink ref="B54" r:id="rId53" xr:uid="{9126161A-8134-8241-9177-DDC3EC71D511}"/>
-    <hyperlink ref="B55" r:id="rId54" xr:uid="{F7A8B56C-ADD9-984A-AC4B-6DA7DC6A4389}"/>
-    <hyperlink ref="B56" r:id="rId55" xr:uid="{E0A8F2A0-C9A8-5249-8CD1-E30BBEEB0A51}"/>
-    <hyperlink ref="B58" r:id="rId56" xr:uid="{50EDE256-2CB6-9A4E-B8A7-B0BBE5499DB8}"/>
-    <hyperlink ref="B57" r:id="rId57" xr:uid="{CE7020DD-E644-D940-A60D-43710686C621}"/>
-    <hyperlink ref="B59" r:id="rId58" xr:uid="{F9F21664-7DC3-8740-9C05-A52C5B200CE9}"/>
+    <hyperlink ref="B59" r:id="rId51" xr:uid="{B1B04A3B-BF2E-FB4F-92FC-CE85A3EDF6E7}"/>
+    <hyperlink ref="B10" r:id="rId52" xr:uid="{55E57EE3-8F32-2D4B-BD9C-0F1971227CB6}"/>
+    <hyperlink ref="B12" r:id="rId53" xr:uid="{9126161A-8134-8241-9177-DDC3EC71D511}"/>
+    <hyperlink ref="B31" r:id="rId54" xr:uid="{F7A8B56C-ADD9-984A-AC4B-6DA7DC6A4389}"/>
+    <hyperlink ref="B32" r:id="rId55" xr:uid="{E0A8F2A0-C9A8-5249-8CD1-E30BBEEB0A51}"/>
+    <hyperlink ref="B36" r:id="rId56" xr:uid="{50EDE256-2CB6-9A4E-B8A7-B0BBE5499DB8}"/>
+    <hyperlink ref="B34" r:id="rId57" xr:uid="{CE7020DD-E644-D940-A60D-43710686C621}"/>
+    <hyperlink ref="B58" r:id="rId58" xr:uid="{F9F21664-7DC3-8740-9C05-A52C5B200CE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
